--- a/card_details.xlsx
+++ b/card_details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dac5049e7ba9ed9/Documents/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C20C120-E634-F746-A4E2-348821D79BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="658" documentId="8_{5C20C120-E634-F746-A4E2-348821D79BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EA130C8-7D49-C546-A6CC-933F1EA8ED59}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2000" windowWidth="17620" windowHeight="20000" xr2:uid="{54D88C54-7615-1740-89B4-7C3E296F3118}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21000" xr2:uid="{54D88C54-7615-1740-89B4-7C3E296F3118}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="446">
   <si>
     <t>Colour</t>
   </si>
@@ -176,9 +176,6 @@
     <t>Shandiz Restaurant</t>
   </si>
   <si>
-    <t>sandiz</t>
-  </si>
-  <si>
     <t>resto</t>
   </si>
   <si>
@@ -194,9 +191,6 @@
     <t>St Martins</t>
   </si>
   <si>
-    <t>the vaughn heritage is strong and we broke into the museum oops!</t>
-  </si>
-  <si>
     <t>Octopus Ice Cream</t>
   </si>
   <si>
@@ -248,9 +242,6 @@
     <t>Kismet Gifts</t>
   </si>
   <si>
-    <t>kismet_gifts</t>
-  </si>
-  <si>
     <t>pink</t>
   </si>
   <si>
@@ -308,9 +299,6 @@
     <t>arte_and_farina</t>
   </si>
   <si>
-    <t>new caron??</t>
-  </si>
-  <si>
     <t>tiny</t>
   </si>
   <si>
@@ -359,9 +347,6 @@
     <t>nd</t>
   </si>
   <si>
-    <t>over priced piercing to support celest</t>
-  </si>
-  <si>
     <t>Tibum Restaurant</t>
   </si>
   <si>
@@ -500,9 +485,6 @@
     <t>USA</t>
   </si>
   <si>
-    <t>lowkey the best clients ever</t>
-  </si>
-  <si>
     <t>Theatre Sainte Catherine</t>
   </si>
   <si>
@@ -581,9 +563,6 @@
     <t>Chez Robin</t>
   </si>
   <si>
-    <t>chez robin</t>
-  </si>
-  <si>
     <t>just popping in for a fun drink</t>
   </si>
   <si>
@@ -605,21 +584,12 @@
     <t xml:space="preserve"> when they say picante they mean it</t>
   </si>
   <si>
-    <t>Denicheuses de Pepites</t>
-  </si>
-  <si>
-    <t>denicheuses_de_pepites</t>
-  </si>
-  <si>
     <t>fyi they do the clothes in café leo</t>
   </si>
   <si>
     <t>Café Bloom</t>
   </si>
   <si>
-    <t>café_bloom</t>
-  </si>
-  <si>
     <t>imagine u n michael here</t>
   </si>
   <si>
@@ -689,21 +659,12 @@
     <t>1/4 tandum jumpers, the luc one</t>
   </si>
   <si>
-    <t>Cafe Sat</t>
-  </si>
-  <si>
-    <t>café_sat</t>
-  </si>
-  <si>
     <t>the first fruity coffee I ever saw, with my papa</t>
   </si>
   <si>
     <t>Carmen Breidy</t>
   </si>
   <si>
-    <t>Cardem Breidy</t>
-  </si>
-  <si>
     <t>mural festivals least impressive art gallery</t>
   </si>
   <si>
@@ -761,9 +722,6 @@
     <t>Sushi Nanami</t>
   </si>
   <si>
-    <t>suchi nanami</t>
-  </si>
-  <si>
     <t>yummy poke bowls</t>
   </si>
   <si>
@@ -827,9 +785,6 @@
     <t>304 Main St, St. Martins, NB E5R 1E5</t>
   </si>
   <si>
-    <t>3677 Rue Jonathan, Laval, QC</t>
-  </si>
-  <si>
     <t>1550 Rue Sainte-Catherine E, Montréal, QC H2L 0J1</t>
   </si>
   <si>
@@ -857,9 +812,6 @@
     <t>251 Rue Dante, Montréal, QC H2S 1K3</t>
   </si>
   <si>
-    <t>Marché Atwater, 138 Atwater Ave, Montreal, Quebec H4C 2H6</t>
-  </si>
-  <si>
     <t>6534 Boul. Saint-Laurent, Montréal, QC H2S 3C6</t>
   </si>
   <si>
@@ -914,9 +866,6 @@
     <t>Amsterdam Brewhouse</t>
   </si>
   <si>
-    <t>South Building, 245 Queens Quay W, Toronto, ON M5J 2K9</t>
-  </si>
-  <si>
     <t>3819 Rue Wellington #102, Verdun, QC H4G 1V1</t>
   </si>
   <si>
@@ -975,13 +924,466 @@
   </si>
   <si>
     <t>2278 Gottingen St, Halifax, NS B3K 0H2</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>2305 Croissant du Sablier, Saint-Lazare, QC J7T 2E2</t>
+  </si>
+  <si>
+    <t>138 Atwater Ave, Montreal, Quebec H4C 2H6</t>
+  </si>
+  <si>
+    <t>1215 Rue Berri, Montréal, QC H2L 0H6</t>
+  </si>
+  <si>
+    <t>245 Queens Quay W, Toronto, ON M5J 2K9</t>
+  </si>
+  <si>
+    <t>159 Rue Saint-Antoine O, Montréal, QC H2Z 2A7</t>
+  </si>
+  <si>
+    <t>564 Reardon Private, Ottawa, ON K1V 2K9</t>
+  </si>
+  <si>
+    <t>502 Carnegie Center Dr Suite 100, Princeton, NJ 08540, United States</t>
+  </si>
+  <si>
+    <t>shandiz</t>
+  </si>
+  <si>
+    <t>chez_robin</t>
+  </si>
+  <si>
+    <t>Pepites de Fripe</t>
+  </si>
+  <si>
+    <t>fripe</t>
+  </si>
+  <si>
+    <t>cafe_bloom</t>
+  </si>
+  <si>
+    <t>cafe_sat</t>
+  </si>
+  <si>
+    <t>cardem_breidy</t>
+  </si>
+  <si>
+    <t>sushi_nanami</t>
+  </si>
+  <si>
+    <t>kismet</t>
+  </si>
+  <si>
+    <t>Rachel Frances</t>
+  </si>
+  <si>
+    <t>rachel_frances</t>
+  </si>
+  <si>
+    <t>a mouse in a coffee shop ?!</t>
+  </si>
+  <si>
+    <t>1030 South Park St Ste 321, Halifax, NS B3H 2W3</t>
+  </si>
+  <si>
+    <t>northern_watters</t>
+  </si>
+  <si>
+    <t>1209 Marginal Rd Unit 115, Halifax, NS B3H 4P8</t>
+  </si>
+  <si>
+    <t>Haliax</t>
+  </si>
+  <si>
+    <t>the clostest thing to the uk in canada</t>
+  </si>
+  <si>
+    <t>The Orange Buoy</t>
+  </si>
+  <si>
+    <t>orange_buoy</t>
+  </si>
+  <si>
+    <t>hailey helped me steal this</t>
+  </si>
+  <si>
+    <t>The Halifax Ghost Walk</t>
+  </si>
+  <si>
+    <t>halifax_ghost_walk</t>
+  </si>
+  <si>
+    <t>1766 Brunswick St, Halifax, NS B3J 3Y3</t>
+  </si>
+  <si>
+    <t>bc you love mysteries :o</t>
+  </si>
+  <si>
+    <t>Cows</t>
+  </si>
+  <si>
+    <t>cows</t>
+  </si>
+  <si>
+    <t>1479 Lower Water St Unit 190, Halifax, NS B3J 3Z3</t>
+  </si>
+  <si>
+    <t>I love moo</t>
+  </si>
+  <si>
+    <t>The Wine Spa</t>
+  </si>
+  <si>
+    <t>wine_spa</t>
+  </si>
+  <si>
+    <t>1447 Hollis St, Halifax, NS B3J 1V1</t>
+  </si>
+  <si>
+    <t>a coupon in case we find our way back!</t>
+  </si>
+  <si>
+    <t>975 Romeo Vachon Blvd N, Dorval, Quebec H4Y 1H1</t>
+  </si>
+  <si>
+    <t>Canada's best airline</t>
+  </si>
+  <si>
+    <t>porter</t>
+  </si>
+  <si>
+    <t>Northern Watters Knitwear &amp; Tartan Shop</t>
+  </si>
+  <si>
+    <t>Porter Airlines</t>
+  </si>
+  <si>
+    <t>Daniel Krauss</t>
+  </si>
+  <si>
+    <t>daniel_krauss</t>
+  </si>
+  <si>
+    <t>Sésame</t>
+  </si>
+  <si>
+    <t>sesame</t>
+  </si>
+  <si>
+    <t>305 Sainte-Catherine St. West, Montreal, Quebec H2X 2A3</t>
+  </si>
+  <si>
+    <t>home of the best fries</t>
+  </si>
+  <si>
+    <t>2451 Rue Bonaventure, Longueuil, QC J4M 1Y5</t>
+  </si>
+  <si>
+    <t>hide your snacks!</t>
+  </si>
+  <si>
+    <t>Association Citoyenne du Village de Montréal</t>
+  </si>
+  <si>
+    <t>acvm</t>
+  </si>
+  <si>
+    <t>1211 Rue Sainte-Catherine E, Montréal, QC H2L 2H1</t>
+  </si>
+  <si>
+    <t>supporting gays all throughout the village</t>
+  </si>
+  <si>
+    <t>katye landry</t>
+  </si>
+  <si>
+    <t>katye</t>
+  </si>
+  <si>
+    <t>Aberdeen Pavilion, Exhibition Way, Ottawa, ON K1S 3W7</t>
+  </si>
+  <si>
+    <t>the designer of your gold mountain necklace</t>
+  </si>
+  <si>
+    <t>Café Le NIGIRIZ</t>
+  </si>
+  <si>
+    <t>cafe_nigiriz</t>
+  </si>
+  <si>
+    <t>32 Rue Saint-Cuthbert, Montreal, Quebec H2W 1L3</t>
+  </si>
+  <si>
+    <t>the clostest onigri to redacted</t>
+  </si>
+  <si>
+    <t>Café Sat</t>
+  </si>
+  <si>
+    <t>RXCHAINGE</t>
+  </si>
+  <si>
+    <t>rxchainge</t>
+  </si>
+  <si>
+    <t>3981 Boul. Saint-Laurent #400, Montreal, Quebec H2W 1Y5</t>
+  </si>
+  <si>
+    <t>redacted's AI</t>
+  </si>
+  <si>
+    <t>ur biggest fan ever</t>
+  </si>
+  <si>
+    <t>over priced piercing to support celeste</t>
+  </si>
+  <si>
+    <t>the vaughn heritage is strong and we broke into the museum... oops!</t>
+  </si>
+  <si>
+    <t>sabor</t>
+  </si>
+  <si>
+    <t>4387 Boul. Saint-Laurent, Montréal, QC H2W 1Z8</t>
+  </si>
+  <si>
+    <t>we got tacos here on one of our first dates :)</t>
+  </si>
+  <si>
+    <t>I thought you'd think this is kewl</t>
+  </si>
+  <si>
+    <t>Paperole</t>
+  </si>
+  <si>
+    <t>Kimono Marie</t>
+  </si>
+  <si>
+    <t>kimono</t>
+  </si>
+  <si>
+    <t>Sabor Latino Saint-Laurent</t>
+  </si>
+  <si>
+    <t>paperole</t>
+  </si>
+  <si>
+    <t>470 Av. Duluth E, Montréal, QC H2L 1A5</t>
+  </si>
+  <si>
+    <t>best place for architecture books and cigarette pencils</t>
+  </si>
+  <si>
+    <t>Palmo Goods</t>
+  </si>
+  <si>
+    <t>5259 Boul. Saint-Laurent, Montréal, QC H2T 1S4</t>
+  </si>
+  <si>
+    <t>Jeans Jeans Jeans</t>
+  </si>
+  <si>
+    <t>jeans</t>
+  </si>
+  <si>
+    <t>5575 Av. Casgrain, Montréal, QC H2T 2A7</t>
+  </si>
+  <si>
+    <t>Beigne Habitude</t>
+  </si>
+  <si>
+    <t>beign_habitude</t>
+  </si>
+  <si>
+    <t>7035 Boul. Saint-Laurent, Montréal, QC H2S 3E3</t>
+  </si>
+  <si>
+    <t>Daddy Roll</t>
+  </si>
+  <si>
+    <t>daddy_roll</t>
+  </si>
+  <si>
+    <t>6527 Boul. Saint-Laurent, Montréal, QC H2S 3C5</t>
+  </si>
+  <si>
+    <t>when they say jeans jeans jeans they mean it</t>
+  </si>
+  <si>
+    <t>one half of the menendez sweet treat taste test</t>
+  </si>
+  <si>
+    <t>other half of the menendez sweet treat taste test</t>
+  </si>
+  <si>
+    <t>we shoulda taken pictures of our renzo sandwiches in the photobooth</t>
+  </si>
+  <si>
+    <t>palmo_goods</t>
+  </si>
+  <si>
+    <t>decisively ok</t>
+  </si>
+  <si>
+    <t>Pourquoi Pas Espresso Bar</t>
+  </si>
+  <si>
+    <t>kink and fetish weekend is in full swing</t>
+  </si>
+  <si>
+    <t>1447 R. Atateken, Montréal, QC H2L 3L2</t>
+  </si>
+  <si>
+    <t>Pigeon Café</t>
+  </si>
+  <si>
+    <t>1301 Rue Sainte-Catherine E, Montréal, QC H2L 2H4</t>
+  </si>
+  <si>
+    <t>Café Parka</t>
+  </si>
+  <si>
+    <t>parka</t>
+  </si>
+  <si>
+    <t>1757 Bd Graham, Mont-Royal, QC H3R 1G7</t>
+  </si>
+  <si>
+    <t>the perfect café with scrumptious chocolate cookie</t>
+  </si>
+  <si>
+    <t>well this is awkward now…</t>
+  </si>
+  <si>
+    <t>1950 Bd Graham, Mont-Royal, QC H3R 1H3</t>
+  </si>
+  <si>
+    <t>mckenna</t>
+  </si>
+  <si>
+    <t>we have to go back to the fancy shop when we finish our phds</t>
+  </si>
+  <si>
+    <t>McKenna Fleuriste</t>
+  </si>
+  <si>
+    <t>Le Parloir</t>
+  </si>
+  <si>
+    <t>Café Cosé</t>
+  </si>
+  <si>
+    <t>Costco Opti-Club</t>
+  </si>
+  <si>
+    <t>23 Rue Bernard O, Montréal, QC H2T 2J6</t>
+  </si>
+  <si>
+    <t>Bernie Beigne</t>
+  </si>
+  <si>
+    <t>bernie</t>
+  </si>
+  <si>
+    <t>u + me + lucy + trey = 4ever</t>
+  </si>
+  <si>
+    <t>parloir</t>
+  </si>
+  <si>
+    <t>cose</t>
+  </si>
+  <si>
+    <t>costco_mtl</t>
+  </si>
+  <si>
+    <t>intro to high tea!</t>
+  </si>
+  <si>
+    <t>4354 Av. Christophe-Colomb, Montréal, QC H2J 3G5</t>
+  </si>
+  <si>
+    <t>1883 Rue Centre, Montréal, QC H3K 1J1</t>
+  </si>
+  <si>
+    <t>300 Rue Bridge, Montréal, QC H3K 2C3</t>
+  </si>
+  <si>
+    <t>do they have a fun latte total?</t>
+  </si>
+  <si>
+    <t>fix your glasses, grab samples, price meat, you can do it all !</t>
+  </si>
+  <si>
+    <t>bsd</t>
+  </si>
+  <si>
+    <t>6966 R. Saint-Denis, Montréal, QC H2S 2S4</t>
+  </si>
+  <si>
+    <t>Bar St-Denis</t>
+  </si>
+  <si>
+    <t>eau-de-vie =/= moscato</t>
+  </si>
+  <si>
+    <t>Pop's Bagel</t>
+  </si>
+  <si>
+    <t>55 E Houston St, New York, NY 10012, United States</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>pops</t>
+  </si>
+  <si>
+    <t>where we are young cher and benjamin franklin</t>
+  </si>
+  <si>
+    <t>30 W 8th St, New York, NY 10011, United States</t>
+  </si>
+  <si>
+    <t>Stumptown Coffee Roasters</t>
+  </si>
+  <si>
+    <t>stumptown</t>
+  </si>
+  <si>
+    <t>with (america) keon and (woke) lily</t>
+  </si>
+  <si>
+    <t>1315 Ontario St E, Montreal, Quebec H2L 1R8</t>
+  </si>
+  <si>
+    <t>Farine &amp; Cacao</t>
+  </si>
+  <si>
+    <t>farine_cacoa</t>
+  </si>
+  <si>
+    <t>tiramasu and chocolate croissant</t>
+  </si>
+  <si>
+    <t>pigeon</t>
+  </si>
+  <si>
+    <t>pourquoi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -989,13 +1391,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1010,9 +1425,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1031,9 +1447,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11F19D0C-C285-2648-B367-B02987B11982}" name="Table1" displayName="Table1" ref="A1:I1048576" totalsRowShown="0">
-  <autoFilter ref="A1:I1048576" xr:uid="{11F19D0C-C285-2648-B367-B02987B11982}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11F19D0C-C285-2648-B367-B02987B11982}" name="Table1" displayName="Table1" ref="A1:K1048576" totalsRowShown="0">
+  <autoFilter ref="A1:K1048576" xr:uid="{11F19D0C-C285-2648-B367-B02987B11982}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K71">
+    <sortCondition ref="A1:A1048576"/>
+  </sortState>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{A9989DE9-E2D4-664C-93BE-FA12AB75A527}" name="Full name"/>
     <tableColumn id="2" xr3:uid="{A086E924-8337-4248-A519-9068FDE554A8}" name="Short name"/>
     <tableColumn id="3" xr3:uid="{0AC17FCB-5BC8-C645-B14A-20F2395ABFAD}" name="Colour"/>
@@ -1043,6 +1462,8 @@
     <tableColumn id="6" xr3:uid="{A2988531-1ACA-4249-8AF7-91295AA9B33E}" name="Date"/>
     <tableColumn id="8" xr3:uid="{F37B8AB4-9EBD-4747-B6D3-6C359F5B0B23}" name="Size"/>
     <tableColumn id="7" xr3:uid="{850C7E7C-59F8-934F-9A24-4D39EB21E323}" name="Notes"/>
+    <tableColumn id="11" xr3:uid="{E1E0ABB2-C2BB-CC4D-8E5C-6BFE3A1F8E2B}" name="Latitude"/>
+    <tableColumn id="12" xr3:uid="{18EE4B38-503A-F947-9343-5FE2C94E9F24}" name="Longitude"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1363,39 +1784,19 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
-  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
-  <we:alternateReferences>
-    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties/>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CA8C31-B4D2-7D40-92D7-389BB1E62C88}">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="40.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1423,216 +1824,264 @@
       <c r="I1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J1" t="s">
+        <v>295</v>
+      </c>
+      <c r="K1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1">
-        <v>46204</v>
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>101</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+      <c r="J2">
+        <v>45.525485699999997</v>
+      </c>
+      <c r="K2">
+        <v>-73.599500199999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>274</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>249</v>
+        <v>300</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>160</v>
       </c>
       <c r="G3" s="1">
-        <v>46204</v>
+        <v>46113</v>
       </c>
       <c r="H3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+      <c r="J3">
+        <v>43.638538400000002</v>
+      </c>
+      <c r="K3">
+        <v>-79.3849965</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1">
         <v>46204</v>
       </c>
       <c r="H4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+      <c r="J4">
+        <v>44.648525399999997</v>
+      </c>
+      <c r="K4">
+        <v>-63.5715881</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
         <v>46204</v>
       </c>
       <c r="H5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+      <c r="J5">
+        <v>45.521327999999997</v>
+      </c>
+      <c r="K5">
+        <v>-73.553268000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="1">
-        <v>46204</v>
+      <c r="G6" t="s">
+        <v>101</v>
       </c>
       <c r="H6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+      <c r="J6">
+        <v>45.539571700000003</v>
+      </c>
+      <c r="K6">
+        <v>-73.623574199999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="1">
-        <v>46204</v>
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>101</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="J7">
+        <v>45.478534600000003</v>
+      </c>
+      <c r="K7">
+        <v>-73.576048200000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>253</v>
+        <v>297</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="G8" s="1">
         <v>46204</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="J8">
+        <v>45.424570000000003</v>
+      </c>
+      <c r="K8">
+        <v>-74.148838100000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -1641,1573 +2090,1897 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="1">
-        <v>46204</v>
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>101</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+      <c r="J9">
+        <v>45.456797999999999</v>
+      </c>
+      <c r="K9">
+        <v>-73.567784000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="G10" s="1">
-        <v>46204</v>
+        <v>46082</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+      <c r="J10">
+        <v>49.278413999999998</v>
+      </c>
+      <c r="K10">
+        <v>-123.1278962</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>308</v>
       </c>
       <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>278</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J11">
+        <v>45.482232199999999</v>
+      </c>
+      <c r="K11">
+        <v>-73.562955700000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>256</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="1">
-        <v>46204</v>
-      </c>
-      <c r="H11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+      <c r="J12">
+        <v>45.509492399999999</v>
+      </c>
+      <c r="K12">
+        <v>-73.562601599999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G13" s="1">
         <v>46204</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="J13">
+        <v>44.644920200000001</v>
+      </c>
+      <c r="K13">
+        <v>-63.573150400000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>207</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>310</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="H14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="J14">
+        <v>45.512964799999999</v>
+      </c>
+      <c r="K14">
+        <v>-73.571314099999995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="1">
-        <v>46204</v>
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
+        <v>101</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+      <c r="J15">
+        <v>45.533387900000001</v>
+      </c>
+      <c r="K15">
+        <v>-73.614319899999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="H16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>211</v>
+      </c>
+      <c r="J16">
+        <v>45.520293000000002</v>
+      </c>
+      <c r="K16">
+        <v>-73.5744799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>305</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="1">
-        <v>46204</v>
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I17" t="s">
+        <v>174</v>
+      </c>
+      <c r="J17">
+        <v>45.4655816</v>
+      </c>
+      <c r="K17">
+        <v>-73.566898100000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>260</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H18" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" t="s">
+        <v>118</v>
+      </c>
+      <c r="J18">
+        <v>45.5164148</v>
+      </c>
+      <c r="K18">
+        <v>-73.577776999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" t="s">
-        <v>252</v>
-      </c>
-      <c r="F18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" s="1">
-        <v>46204</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>301</v>
+      </c>
+      <c r="F19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" t="s">
+        <v>157</v>
+      </c>
+      <c r="J19">
+        <v>45.505674165524297</v>
+      </c>
+      <c r="K19">
+        <v>-73.559802050331697</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>306</v>
+      </c>
+      <c r="B20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
+        <v>299</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H20" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" t="s">
+        <v>181</v>
+      </c>
+      <c r="J20">
+        <v>45.514262799999997</v>
+      </c>
+      <c r="K20">
+        <v>-73.558441500000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
         <v>58</v>
       </c>
-      <c r="I18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" t="s">
-        <v>262</v>
-      </c>
-      <c r="F19" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="1">
-        <v>46204</v>
-      </c>
-      <c r="H19" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" t="s">
-        <v>263</v>
-      </c>
-      <c r="F20" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" s="1">
-        <v>46204</v>
-      </c>
-      <c r="H20" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>264</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="E21" t="s">
+        <v>287</v>
+      </c>
+      <c r="F21" t="s">
+        <v>214</v>
+      </c>
+      <c r="G21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H21" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" t="s">
+        <v>215</v>
+      </c>
+      <c r="J21">
+        <v>53.551524000000001</v>
+      </c>
+      <c r="K21">
+        <v>-113.5363093</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" t="s">
         <v>265</v>
       </c>
-      <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" t="s">
-        <v>266</v>
-      </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="1">
-        <v>46204</v>
-      </c>
-      <c r="H21" t="s">
-        <v>90</v>
-      </c>
-      <c r="I21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" t="s">
-        <v>267</v>
-      </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="G22" s="1">
-        <v>46204</v>
+        <v>46082</v>
       </c>
       <c r="H22" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="J22">
+        <v>49.281593600000001</v>
+      </c>
+      <c r="K22">
+        <v>-123.12375400000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>222</v>
       </c>
       <c r="C23" t="s">
         <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
       </c>
-      <c r="G23" s="1">
-        <v>46204</v>
+      <c r="G23" t="s">
+        <v>101</v>
       </c>
       <c r="H23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+      <c r="J23">
+        <v>45.538747000000001</v>
+      </c>
+      <c r="K23">
+        <v>-73.617334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>292</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="G24" s="1">
+        <v>46113</v>
+      </c>
+      <c r="H24" t="s">
+        <v>54</v>
+      </c>
+      <c r="I24" t="s">
+        <v>225</v>
+      </c>
+      <c r="J24">
+        <v>43.666613699999999</v>
+      </c>
+      <c r="K24">
+        <v>-79.315919500000007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" t="s">
+        <v>257</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
+        <v>101</v>
+      </c>
+      <c r="H25" t="s">
+        <v>54</v>
+      </c>
+      <c r="I25" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25">
+        <v>45.5307855</v>
+      </c>
+      <c r="K25">
+        <v>-73.610190700000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" t="s">
+        <v>259</v>
+      </c>
+      <c r="F26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="1">
         <v>46174</v>
       </c>
-      <c r="H24" t="s">
-        <v>56</v>
-      </c>
-      <c r="I24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>103</v>
-      </c>
-      <c r="B25" t="s">
-        <v>104</v>
-      </c>
-      <c r="C25" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" t="s">
-        <v>270</v>
-      </c>
-      <c r="F25" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" t="s">
-        <v>105</v>
-      </c>
-      <c r="H25" t="s">
-        <v>56</v>
-      </c>
-      <c r="I25" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" t="s">
-        <v>271</v>
-      </c>
-      <c r="F26" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" t="s">
-        <v>105</v>
-      </c>
       <c r="H26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="J26">
+        <v>45.646497500000002</v>
+      </c>
+      <c r="K26">
+        <v>-74.950319699999994</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="F27" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" t="s">
-        <v>105</v>
+        <v>125</v>
+      </c>
+      <c r="G27" s="1">
+        <v>46174</v>
       </c>
       <c r="H27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I27" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+      <c r="J27">
+        <v>45.646497500000002</v>
+      </c>
+      <c r="K27">
+        <v>-74.950319699999994</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="F28" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" t="s">
-        <v>105</v>
+        <v>11</v>
+      </c>
+      <c r="G28" s="1">
+        <v>46204</v>
       </c>
       <c r="H28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I28" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+      <c r="J28">
+        <v>44.610066000000003</v>
+      </c>
+      <c r="K28">
+        <v>-63.493685999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" t="s">
+        <v>276</v>
+      </c>
+      <c r="F29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" t="s">
         <v>101</v>
       </c>
-      <c r="D29" t="s">
-        <v>46</v>
-      </c>
-      <c r="E29" t="s">
-        <v>274</v>
-      </c>
-      <c r="F29" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" s="1">
-        <v>45413</v>
-      </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+      <c r="J29">
+        <v>45.538747000000001</v>
+      </c>
+      <c r="K29">
+        <v>-73.617334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" t="s">
+        <v>245</v>
+      </c>
+      <c r="F30" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H30" t="s">
+        <v>54</v>
+      </c>
+      <c r="I30" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30">
+        <v>44.645773800000001</v>
+      </c>
+      <c r="K30">
+        <v>-63.570199799999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" t="s">
+        <v>204</v>
+      </c>
+      <c r="E31" t="s">
+        <v>302</v>
+      </c>
+      <c r="F31" t="s">
+        <v>200</v>
+      </c>
+      <c r="G31" t="s">
         <v>101</v>
       </c>
-      <c r="D30" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" t="s">
-        <v>275</v>
-      </c>
-      <c r="F30" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" s="1">
-        <v>46174</v>
-      </c>
-      <c r="H30" t="s">
-        <v>56</v>
-      </c>
-      <c r="I30" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>121</v>
-      </c>
-      <c r="B31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" t="s">
-        <v>276</v>
-      </c>
-      <c r="F31" t="s">
-        <v>30</v>
-      </c>
-      <c r="G31" t="s">
-        <v>105</v>
-      </c>
       <c r="H31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I31" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+      <c r="J31">
+        <v>45.374880246000501</v>
+      </c>
+      <c r="K31">
+        <v>-75.648204758528294</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="F32" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="G32" s="1">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="H32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I32" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+      <c r="J32">
+        <v>43.656252100000003</v>
+      </c>
+      <c r="K32">
+        <v>-79.3996475</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="F33" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="G33" s="1">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="H33" t="s">
         <v>56</v>
       </c>
       <c r="I33" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="J33">
+        <v>44.636329699999997</v>
+      </c>
+      <c r="K33">
+        <v>-63.565745300000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
       </c>
-      <c r="G34" t="s">
-        <v>105</v>
+      <c r="G34" s="1">
+        <v>46204</v>
       </c>
       <c r="H34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I34" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+      <c r="J34">
+        <v>45.514992300000003</v>
+      </c>
+      <c r="K34">
+        <v>-73.575328900000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
         <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
       </c>
-      <c r="G35" t="s">
-        <v>105</v>
+      <c r="G35" s="1">
+        <v>46204</v>
       </c>
       <c r="H35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I35" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+      <c r="J35">
+        <v>45.509827799999997</v>
+      </c>
+      <c r="K35">
+        <v>-73.564386299999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
-      </c>
-      <c r="G36" t="s">
-        <v>105</v>
+        <v>11</v>
+      </c>
+      <c r="G36" s="1">
+        <v>46204</v>
       </c>
       <c r="H36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I36" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="J36">
+        <v>44.610066000000003</v>
+      </c>
+      <c r="K36">
+        <v>-63.493685999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="F37" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="G37" s="1">
-        <v>46082</v>
+        <v>46204</v>
       </c>
       <c r="H37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="J37">
+        <v>45.354297000000003</v>
+      </c>
+      <c r="K37">
+        <v>-65.537473000000006</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="F38" t="s">
         <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H38" t="s">
+        <v>54</v>
+      </c>
+      <c r="I38" t="s">
+        <v>133</v>
+      </c>
+      <c r="J38">
+        <v>45.518610384488298</v>
+      </c>
+      <c r="K38">
+        <v>-73.558040084524094</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" t="s">
+        <v>312</v>
+      </c>
+      <c r="C39" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" t="s">
+        <v>246</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H39" t="s">
         <v>56</v>
       </c>
-      <c r="I38" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="I39" t="s">
+        <v>68</v>
+      </c>
+      <c r="J39">
+        <v>44.6104427</v>
+      </c>
+      <c r="K39">
+        <v>-63.494387000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" t="s">
+        <v>237</v>
+      </c>
+      <c r="F40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H40" t="s">
+        <v>54</v>
+      </c>
+      <c r="I40" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40">
+        <v>45.482875999999997</v>
+      </c>
+      <c r="K40">
+        <v>-73.579100999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" t="s">
+        <v>236</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H41" t="s">
+        <v>54</v>
+      </c>
+      <c r="I41" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41">
+        <v>44.609839999999998</v>
+      </c>
+      <c r="K41">
+        <v>-63.493228999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" t="s">
+        <v>147</v>
+      </c>
+      <c r="G42" t="s">
+        <v>101</v>
+      </c>
+      <c r="H42" t="s">
+        <v>54</v>
+      </c>
+      <c r="I42" t="s">
+        <v>205</v>
+      </c>
+      <c r="J42" t="s">
+        <v>254</v>
+      </c>
+      <c r="K42" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>145</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B43" t="s">
         <v>146</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C43" t="s">
         <v>10</v>
       </c>
-      <c r="D39" t="s">
-        <v>97</v>
-      </c>
-      <c r="E39" t="s">
-        <v>283</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="D43" t="s">
+        <v>204</v>
+      </c>
+      <c r="E43" t="s">
+        <v>303</v>
+      </c>
+      <c r="F43" t="s">
         <v>147</v>
       </c>
-      <c r="G39" s="1">
-        <v>46082</v>
-      </c>
-      <c r="H39" t="s">
-        <v>148</v>
-      </c>
-      <c r="I39" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>150</v>
-      </c>
-      <c r="B40" t="s">
-        <v>151</v>
-      </c>
-      <c r="C40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" t="s">
-        <v>214</v>
-      </c>
-      <c r="E40" t="s">
-        <v>269</v>
-      </c>
-      <c r="F40" t="s">
-        <v>152</v>
-      </c>
-      <c r="G40" t="s">
-        <v>105</v>
-      </c>
-      <c r="H40" t="s">
-        <v>56</v>
-      </c>
-      <c r="I40" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" t="s">
-        <v>155</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="G43" t="s">
+        <v>101</v>
+      </c>
+      <c r="H43" t="s">
+        <v>54</v>
+      </c>
+      <c r="I43" t="s">
+        <v>366</v>
+      </c>
+      <c r="J43">
+        <v>40.314159841377702</v>
+      </c>
+      <c r="K43">
+        <v>-74.653873622460495</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B44" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" t="s">
+        <v>273</v>
+      </c>
+      <c r="F44" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" t="s">
+        <v>101</v>
+      </c>
+      <c r="H44" t="s">
+        <v>54</v>
+      </c>
+      <c r="I44" t="s">
+        <v>170</v>
+      </c>
+      <c r="J44">
+        <v>45.456797999999999</v>
+      </c>
+      <c r="K44">
+        <v>-73.567784000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" t="s">
+        <v>238</v>
+      </c>
+      <c r="F45" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H45" t="s">
+        <v>54</v>
+      </c>
+      <c r="I45" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45">
+        <v>44.636415</v>
+      </c>
+      <c r="K45">
+        <v>-63.565404000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" t="s">
         <v>80</v>
       </c>
-      <c r="D41" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" t="s">
-        <v>284</v>
-      </c>
-      <c r="F41" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" t="s">
-        <v>105</v>
-      </c>
-      <c r="H41" t="s">
-        <v>56</v>
-      </c>
-      <c r="I41" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>157</v>
-      </c>
-      <c r="B42" t="s">
-        <v>158</v>
-      </c>
-      <c r="C42" t="s">
-        <v>66</v>
-      </c>
-      <c r="D42" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" t="s">
-        <v>285</v>
-      </c>
-      <c r="F42" t="s">
-        <v>159</v>
-      </c>
-      <c r="G42" s="1">
-        <v>46113</v>
-      </c>
-      <c r="H42" t="s">
-        <v>56</v>
-      </c>
-      <c r="I42" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" t="s">
-        <v>162</v>
-      </c>
-      <c r="C43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43" t="s">
-        <v>29</v>
-      </c>
-      <c r="E43" t="s">
-        <v>269</v>
-      </c>
-      <c r="F43" t="s">
-        <v>30</v>
-      </c>
-      <c r="G43" t="s">
-        <v>105</v>
-      </c>
-      <c r="H43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I43" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>164</v>
-      </c>
-      <c r="B44" t="s">
-        <v>165</v>
-      </c>
-      <c r="C44" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" t="s">
-        <v>286</v>
-      </c>
-      <c r="F44" t="s">
-        <v>166</v>
-      </c>
-      <c r="G44" s="1">
-        <v>46113</v>
-      </c>
-      <c r="H44" t="s">
-        <v>56</v>
-      </c>
-      <c r="I44" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>168</v>
-      </c>
-      <c r="B45" t="s">
-        <v>169</v>
-      </c>
-      <c r="C45" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45" t="s">
-        <v>97</v>
-      </c>
-      <c r="E45" t="s">
-        <v>287</v>
-      </c>
-      <c r="F45" t="s">
-        <v>30</v>
-      </c>
-      <c r="G45" t="s">
-        <v>105</v>
-      </c>
-      <c r="H45" t="s">
-        <v>56</v>
-      </c>
-      <c r="I45" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>171</v>
-      </c>
-      <c r="B46" t="s">
-        <v>172</v>
-      </c>
-      <c r="C46" t="s">
-        <v>66</v>
-      </c>
       <c r="D46" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="F46" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G46" s="1">
         <v>46082</v>
       </c>
       <c r="H46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I46" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+      <c r="J46">
+        <v>49.289905099999999</v>
+      </c>
+      <c r="K46">
+        <v>-123.1380932</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E47" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="F47" t="s">
         <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H47" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I47" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+      <c r="J47">
+        <v>45.529071999999999</v>
+      </c>
+      <c r="K47">
+        <v>-73.578416000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>290</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="E48" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="F48" t="s">
-        <v>166</v>
-      </c>
-      <c r="G48" s="1">
-        <v>46113</v>
+        <v>30</v>
+      </c>
+      <c r="G48" t="s">
+        <v>101</v>
       </c>
       <c r="H48" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I48" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+        <v>367</v>
+      </c>
+      <c r="J48">
+        <v>45.520293000000002</v>
+      </c>
+      <c r="K48">
+        <v>-73.5744799</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>179</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E49" t="s">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="F49" t="s">
-        <v>30</v>
-      </c>
-      <c r="G49" t="s">
-        <v>105</v>
+        <v>49</v>
+      </c>
+      <c r="G49" s="1">
+        <v>46204</v>
       </c>
       <c r="H49" t="s">
         <v>56</v>
       </c>
       <c r="I49" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="J49">
+        <v>45.350248999999998</v>
+      </c>
+      <c r="K49">
+        <v>-65.550083000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>182</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D50" t="s">
         <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="F50" t="s">
-        <v>30</v>
-      </c>
-      <c r="G50" t="s">
-        <v>105</v>
+        <v>49</v>
+      </c>
+      <c r="G50" s="1">
+        <v>46204</v>
       </c>
       <c r="H50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I50" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="J50">
+        <v>45.354297000000003</v>
+      </c>
+      <c r="K50">
+        <v>-65.537473000000006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="B51" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C51" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="F51" t="s">
         <v>30</v>
       </c>
-      <c r="G51" t="s">
-        <v>105</v>
+      <c r="G51" s="2">
+        <v>45530</v>
       </c>
       <c r="H51" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I51" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+      <c r="J51">
+        <v>45.537944099999997</v>
+      </c>
+      <c r="K51">
+        <v>-73.613300600000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="F52" t="s">
         <v>30</v>
       </c>
-      <c r="G52" t="s">
-        <v>105</v>
+      <c r="G52" s="1">
+        <v>46204</v>
       </c>
       <c r="H52" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="J52">
+        <v>45.510855399999997</v>
+      </c>
+      <c r="K52">
+        <v>-73.566595699999993</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="B53" t="s">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E53" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="F53" t="s">
         <v>30</v>
       </c>
       <c r="G53" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H53" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I53" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+      <c r="J53">
+        <v>45.514280800000002</v>
+      </c>
+      <c r="K53">
+        <v>-73.573992099999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>296</v>
+        <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>194</v>
+        <v>48</v>
       </c>
       <c r="C54" t="s">
         <v>42</v>
       </c>
       <c r="D54" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" t="s">
+        <v>242</v>
+      </c>
+      <c r="F54" t="s">
+        <v>49</v>
+      </c>
+      <c r="G54" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H54" t="s">
+        <v>54</v>
+      </c>
+      <c r="I54" t="s">
+        <v>368</v>
+      </c>
+      <c r="J54">
+        <v>45.353083499999997</v>
+      </c>
+      <c r="K54">
+        <v>-65.540429599999996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>228</v>
+      </c>
+      <c r="B55" t="s">
+        <v>229</v>
+      </c>
+      <c r="C55" t="s">
         <v>97</v>
       </c>
-      <c r="E54" t="s">
-        <v>297</v>
-      </c>
-      <c r="F54" t="s">
-        <v>30</v>
-      </c>
-      <c r="G54" t="s">
-        <v>105</v>
-      </c>
-      <c r="H54" t="s">
-        <v>58</v>
-      </c>
-      <c r="I54" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>196</v>
-      </c>
-      <c r="B55" t="s">
-        <v>197</v>
-      </c>
-      <c r="C55" t="s">
-        <v>42</v>
-      </c>
       <c r="D55" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F55" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G55" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I55" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+        <v>230</v>
+      </c>
+      <c r="J55">
+        <v>44.653763400000003</v>
+      </c>
+      <c r="K55">
+        <v>-63.586178400000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="B56" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="C56" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D56" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="F56" t="s">
-        <v>30</v>
-      </c>
-      <c r="G56" t="s">
-        <v>105</v>
+        <v>153</v>
+      </c>
+      <c r="G56" s="1">
+        <v>46113</v>
       </c>
       <c r="H56" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I56" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="J56">
+        <v>44.587119199999997</v>
+      </c>
+      <c r="K56">
+        <v>-75.689283500000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="B57" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C57" t="s">
         <v>42</v>
       </c>
       <c r="D57" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" t="s">
+        <v>289</v>
+      </c>
+      <c r="F57" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57" t="s">
+        <v>101</v>
+      </c>
+      <c r="H57" t="s">
+        <v>54</v>
+      </c>
+      <c r="I57" t="s">
+        <v>217</v>
+      </c>
+      <c r="J57">
+        <v>45.483075999999997</v>
+      </c>
+      <c r="K57">
+        <v>-73.575241000000005</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" t="s">
+        <v>241</v>
+      </c>
+      <c r="F58" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H58" t="s">
+        <v>55</v>
+      </c>
+      <c r="I58" t="s">
+        <v>46</v>
+      </c>
+      <c r="J58">
+        <v>44.655426300000002</v>
+      </c>
+      <c r="K58">
+        <v>-63.593388400000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
         <v>22</v>
       </c>
-      <c r="E57" t="s">
-        <v>300</v>
-      </c>
-      <c r="F57" t="s">
-        <v>30</v>
-      </c>
-      <c r="G57" t="s">
-        <v>105</v>
-      </c>
-      <c r="H57" t="s">
-        <v>56</v>
-      </c>
-      <c r="I57" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>205</v>
-      </c>
-      <c r="B58" t="s">
-        <v>206</v>
-      </c>
-      <c r="C58" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" t="s">
-        <v>29</v>
-      </c>
-      <c r="E58" t="s">
-        <v>301</v>
-      </c>
-      <c r="F58" t="s">
-        <v>30</v>
-      </c>
-      <c r="G58" t="s">
-        <v>105</v>
-      </c>
-      <c r="H58" t="s">
-        <v>56</v>
-      </c>
-      <c r="I58" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>208</v>
-      </c>
-      <c r="B59" t="s">
-        <v>209</v>
-      </c>
-      <c r="C59" t="s">
-        <v>42</v>
-      </c>
-      <c r="D59" t="s">
-        <v>214</v>
-      </c>
       <c r="E59" t="s">
-        <v>269</v>
+        <v>234</v>
       </c>
       <c r="F59" t="s">
-        <v>210</v>
-      </c>
-      <c r="G59" t="s">
-        <v>105</v>
+        <v>11</v>
+      </c>
+      <c r="G59" s="1">
+        <v>46204</v>
       </c>
       <c r="H59" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I59" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="J59">
+        <v>44.610039</v>
+      </c>
+      <c r="K59">
+        <v>-63.493564999999997</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="D60" t="s">
-        <v>214</v>
+        <v>45</v>
       </c>
       <c r="E60" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="F60" t="s">
-        <v>152</v>
-      </c>
-      <c r="G60" t="s">
-        <v>105</v>
+        <v>30</v>
+      </c>
+      <c r="G60" s="1">
+        <v>45413</v>
       </c>
       <c r="H60" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I60" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+      <c r="J60">
+        <v>45.496544</v>
+      </c>
+      <c r="K60">
+        <v>-73.572867000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="B61" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C61" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E61" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
       </c>
-      <c r="G61" s="1">
-        <v>46174</v>
+      <c r="G61" t="s">
+        <v>101</v>
       </c>
       <c r="H61" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I61" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+      <c r="J61">
+        <v>45.512327999999997</v>
+      </c>
+      <c r="K61">
+        <v>-73.561437999999995</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B62" t="s">
-        <v>220</v>
+        <v>311</v>
       </c>
       <c r="C62" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="E62" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
       </c>
-      <c r="G62" s="1">
-        <v>46174</v>
+      <c r="G62" t="s">
+        <v>101</v>
       </c>
       <c r="H62" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I62" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+        <v>227</v>
+      </c>
+      <c r="J62">
+        <v>45.537235000000003</v>
+      </c>
+      <c r="K62">
+        <v>-73.615161000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>222</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
-        <v>223</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E63" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
@@ -3216,242 +3989,1416 @@
         <v>46174</v>
       </c>
       <c r="H63" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I63" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+      <c r="J63" t="s">
+        <v>254</v>
+      </c>
+      <c r="K63" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>225</v>
+        <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>226</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" t="s">
+        <v>244</v>
+      </c>
+      <c r="F64" t="s">
+        <v>49</v>
+      </c>
+      <c r="G64" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H64" t="s">
+        <v>55</v>
+      </c>
+      <c r="I64" t="s">
+        <v>61</v>
+      </c>
+      <c r="J64">
+        <v>45.354367000000003</v>
+      </c>
+      <c r="K64">
+        <v>-65.543087999999997</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" t="s">
+        <v>77</v>
+      </c>
+      <c r="D65" t="s">
+        <v>34</v>
+      </c>
+      <c r="E65" t="s">
+        <v>268</v>
+      </c>
+      <c r="F65" t="s">
+        <v>30</v>
+      </c>
+      <c r="G65" t="s">
+        <v>101</v>
+      </c>
+      <c r="H65" t="s">
+        <v>54</v>
+      </c>
+      <c r="I65" t="s">
+        <v>150</v>
+      </c>
+      <c r="J65">
+        <v>45.512327999999997</v>
+      </c>
+      <c r="K65">
+        <v>-73.561437999999995</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>102</v>
+      </c>
+      <c r="B66" t="s">
+        <v>103</v>
+      </c>
+      <c r="C66" t="s">
+        <v>97</v>
+      </c>
+      <c r="D66" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" t="s">
+        <v>256</v>
+      </c>
+      <c r="F66" t="s">
+        <v>30</v>
+      </c>
+      <c r="G66" t="s">
+        <v>101</v>
+      </c>
+      <c r="H66" t="s">
+        <v>54</v>
+      </c>
+      <c r="I66" t="s">
+        <v>104</v>
+      </c>
+      <c r="J66">
+        <v>45.5350374</v>
+      </c>
+      <c r="K66">
+        <v>-73.611998200000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67" t="s">
+        <v>267</v>
+      </c>
+      <c r="F67" t="s">
+        <v>142</v>
+      </c>
+      <c r="G67" s="1">
+        <v>46082</v>
+      </c>
+      <c r="H67" t="s">
+        <v>143</v>
+      </c>
+      <c r="I67" t="s">
+        <v>144</v>
+      </c>
+      <c r="J67">
+        <v>20.598514758979</v>
+      </c>
+      <c r="K67">
+        <v>-105.238483153597</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>279</v>
+      </c>
+      <c r="B68" t="s">
+        <v>184</v>
+      </c>
+      <c r="C68" t="s">
         <v>42</v>
       </c>
-      <c r="D64" t="s">
-        <v>60</v>
-      </c>
-      <c r="E64" t="s">
-        <v>304</v>
-      </c>
-      <c r="F64" t="s">
-        <v>227</v>
-      </c>
-      <c r="G64" t="s">
-        <v>105</v>
-      </c>
-      <c r="H64" t="s">
-        <v>56</v>
-      </c>
-      <c r="I64" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>305</v>
-      </c>
-      <c r="B65" t="s">
-        <v>229</v>
-      </c>
-      <c r="C65" t="s">
-        <v>42</v>
-      </c>
-      <c r="D65" t="s">
-        <v>29</v>
-      </c>
-      <c r="E65" t="s">
-        <v>306</v>
-      </c>
-      <c r="F65" t="s">
-        <v>30</v>
-      </c>
-      <c r="G65" t="s">
-        <v>105</v>
-      </c>
-      <c r="H65" t="s">
-        <v>56</v>
-      </c>
-      <c r="I65" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>231</v>
-      </c>
-      <c r="B66" t="s">
-        <v>232</v>
-      </c>
-      <c r="C66" t="s">
-        <v>42</v>
-      </c>
-      <c r="D66" t="s">
-        <v>22</v>
-      </c>
-      <c r="E66" t="s">
-        <v>307</v>
-      </c>
-      <c r="F66" t="s">
-        <v>30</v>
-      </c>
-      <c r="G66" t="s">
-        <v>105</v>
-      </c>
-      <c r="H66" t="s">
-        <v>56</v>
-      </c>
-      <c r="I66" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>234</v>
-      </c>
-      <c r="B67" t="s">
-        <v>235</v>
-      </c>
-      <c r="C67" t="s">
-        <v>42</v>
-      </c>
-      <c r="D67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E67" t="s">
-        <v>293</v>
-      </c>
-      <c r="F67" t="s">
-        <v>30</v>
-      </c>
-      <c r="G67" t="s">
-        <v>105</v>
-      </c>
-      <c r="H67" t="s">
-        <v>56</v>
-      </c>
-      <c r="I67" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>309</v>
-      </c>
-      <c r="B68" t="s">
-        <v>237</v>
-      </c>
-      <c r="C68" t="s">
-        <v>83</v>
-      </c>
       <c r="D68" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="E68" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="F68" t="s">
-        <v>166</v>
-      </c>
-      <c r="G68" s="1">
-        <v>46113</v>
+        <v>30</v>
+      </c>
+      <c r="G68" t="s">
+        <v>101</v>
       </c>
       <c r="H68" t="s">
         <v>56</v>
       </c>
       <c r="I68" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+      <c r="J68">
+        <v>45.516409000000003</v>
+      </c>
+      <c r="K68">
+        <v>-73.554338999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="B69" t="s">
-        <v>240</v>
+        <v>163</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="E69" t="s">
-        <v>310</v>
+        <v>271</v>
       </c>
       <c r="F69" t="s">
         <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H69" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I69" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="J69">
+        <v>45.489068600000003</v>
+      </c>
+      <c r="K69">
+        <v>-73.585808599999993</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="B70" t="s">
+        <v>190</v>
+      </c>
+      <c r="C70" t="s">
+        <v>42</v>
+      </c>
+      <c r="D70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" t="s">
+        <v>282</v>
+      </c>
+      <c r="F70" t="s">
+        <v>30</v>
+      </c>
+      <c r="G70" t="s">
+        <v>101</v>
+      </c>
+      <c r="H70" t="s">
+        <v>54</v>
+      </c>
+      <c r="I70" t="s">
+        <v>191</v>
+      </c>
+      <c r="J70">
+        <v>45.520066</v>
+      </c>
+      <c r="K70">
+        <v>-73.595687999999996</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>192</v>
+      </c>
+      <c r="B71" t="s">
+        <v>193</v>
+      </c>
+      <c r="C71" t="s">
+        <v>42</v>
+      </c>
+      <c r="D71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" t="s">
+        <v>283</v>
+      </c>
+      <c r="F71" t="s">
+        <v>30</v>
+      </c>
+      <c r="G71" t="s">
+        <v>101</v>
+      </c>
+      <c r="H71" t="s">
+        <v>54</v>
+      </c>
+      <c r="I71" t="s">
+        <v>194</v>
+      </c>
+      <c r="J71">
+        <v>45.532531900000002</v>
+      </c>
+      <c r="K71">
+        <v>-73.614110499999995</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>313</v>
+      </c>
+      <c r="B72" t="s">
+        <v>314</v>
+      </c>
+      <c r="C72" t="s">
+        <v>67</v>
+      </c>
+      <c r="D72" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" t="s">
+        <v>316</v>
+      </c>
+      <c r="F72" t="s">
+        <v>35</v>
+      </c>
+      <c r="G72" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H72" t="s">
+        <v>54</v>
+      </c>
+      <c r="I72" t="s">
+        <v>315</v>
+      </c>
+      <c r="J72">
+        <v>44.636038158292799</v>
+      </c>
+      <c r="K72">
+        <v>-63.576597290380398</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>339</v>
+      </c>
+      <c r="B73" t="s">
+        <v>317</v>
+      </c>
+      <c r="C73" t="s">
+        <v>52</v>
+      </c>
+      <c r="D73" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" t="s">
+        <v>318</v>
+      </c>
+      <c r="F73" t="s">
+        <v>319</v>
+      </c>
+      <c r="G73" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H73" t="s">
+        <v>54</v>
+      </c>
+      <c r="I73" t="s">
+        <v>320</v>
+      </c>
+      <c r="J73">
+        <v>44.6432107892483</v>
+      </c>
+      <c r="K73">
+        <v>-63.565810365598601</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>321</v>
+      </c>
+      <c r="B74" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" t="s">
         <v>243</v>
       </c>
-      <c r="C70" t="s">
+      <c r="F74" t="s">
+        <v>49</v>
+      </c>
+      <c r="G74" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H74" t="s">
+        <v>54</v>
+      </c>
+      <c r="I74" t="s">
+        <v>323</v>
+      </c>
+      <c r="J74">
+        <v>45.359008986650501</v>
+      </c>
+      <c r="K74">
+        <v>-65.532744335887202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>324</v>
+      </c>
+      <c r="B75" t="s">
+        <v>325</v>
+      </c>
+      <c r="C75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" t="s">
+        <v>34</v>
+      </c>
+      <c r="E75" t="s">
+        <v>326</v>
+      </c>
+      <c r="F75" t="s">
+        <v>35</v>
+      </c>
+      <c r="G75" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H75" t="s">
+        <v>54</v>
+      </c>
+      <c r="I75" t="s">
+        <v>327</v>
+      </c>
+      <c r="J75">
+        <v>44.6475375031238</v>
+      </c>
+      <c r="K75">
+        <v>-63.577567608695396</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>328</v>
+      </c>
+      <c r="B76" t="s">
+        <v>329</v>
+      </c>
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" t="s">
+        <v>58</v>
+      </c>
+      <c r="E76" t="s">
+        <v>330</v>
+      </c>
+      <c r="F76" t="s">
+        <v>319</v>
+      </c>
+      <c r="G76" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H76" t="s">
+        <v>54</v>
+      </c>
+      <c r="I76" t="s">
+        <v>331</v>
+      </c>
+      <c r="J76">
+        <v>44.645134706114099</v>
+      </c>
+      <c r="K76">
+        <v>-63.568191159293796</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>332</v>
+      </c>
+      <c r="B77" t="s">
+        <v>333</v>
+      </c>
+      <c r="C77" t="s">
+        <v>52</v>
+      </c>
+      <c r="D77" t="s">
+        <v>93</v>
+      </c>
+      <c r="E77" t="s">
+        <v>334</v>
+      </c>
+      <c r="F77" t="s">
+        <v>319</v>
+      </c>
+      <c r="G77" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H77" t="s">
+        <v>54</v>
+      </c>
+      <c r="I77" t="s">
+        <v>335</v>
+      </c>
+      <c r="J77">
+        <v>44.643751014574804</v>
+      </c>
+      <c r="K77">
+        <v>-63.570560930618399</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>340</v>
+      </c>
+      <c r="B78" t="s">
+        <v>338</v>
+      </c>
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" t="s">
+        <v>93</v>
+      </c>
+      <c r="E78" t="s">
+        <v>336</v>
+      </c>
+      <c r="F78" t="s">
+        <v>30</v>
+      </c>
+      <c r="G78" t="s">
         <v>101</v>
       </c>
-      <c r="D70" t="s">
-        <v>46</v>
-      </c>
-      <c r="E70" t="s">
-        <v>311</v>
-      </c>
-      <c r="F70" t="s">
-        <v>35</v>
-      </c>
-      <c r="G70" t="s">
-        <v>105</v>
-      </c>
-      <c r="H70" t="s">
-        <v>56</v>
-      </c>
-      <c r="I70" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>245</v>
-      </c>
-      <c r="B71" t="s">
-        <v>246</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="H78" t="s">
+        <v>54</v>
+      </c>
+      <c r="I78" t="s">
+        <v>337</v>
+      </c>
+      <c r="J78">
+        <v>45.466528144373598</v>
+      </c>
+      <c r="K78">
+        <v>-73.745059523561906</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>341</v>
+      </c>
+      <c r="B79" t="s">
+        <v>342</v>
+      </c>
+      <c r="C79" t="s">
+        <v>80</v>
+      </c>
+      <c r="D79" t="s">
+        <v>204</v>
+      </c>
+      <c r="E79" t="s">
+        <v>347</v>
+      </c>
+      <c r="F79" t="s">
+        <v>30</v>
+      </c>
+      <c r="G79" t="s">
+        <v>101</v>
+      </c>
+      <c r="H79" t="s">
+        <v>54</v>
+      </c>
+      <c r="I79" t="s">
+        <v>348</v>
+      </c>
+      <c r="J79">
+        <v>45.543149197762901</v>
+      </c>
+      <c r="K79">
+        <v>-73.452520193901094</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>343</v>
+      </c>
+      <c r="B80" t="s">
+        <v>344</v>
+      </c>
+      <c r="C80" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" t="s">
+        <v>345</v>
+      </c>
+      <c r="F80" t="s">
+        <v>30</v>
+      </c>
+      <c r="G80" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H80" t="s">
+        <v>54</v>
+      </c>
+      <c r="I80" t="s">
+        <v>346</v>
+      </c>
+      <c r="J80">
+        <v>45.506976522127502</v>
+      </c>
+      <c r="K80">
+        <v>-73.566848154775499</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>349</v>
+      </c>
+      <c r="B81" t="s">
+        <v>350</v>
+      </c>
+      <c r="C81" t="s">
+        <v>67</v>
+      </c>
+      <c r="D81" t="s">
+        <v>204</v>
+      </c>
+      <c r="E81" t="s">
+        <v>351</v>
+      </c>
+      <c r="F81" t="s">
+        <v>30</v>
+      </c>
+      <c r="G81" t="s">
+        <v>101</v>
+      </c>
+      <c r="H81" t="s">
+        <v>54</v>
+      </c>
+      <c r="I81" t="s">
+        <v>352</v>
+      </c>
+      <c r="J81">
+        <v>45.518793896594701</v>
+      </c>
+      <c r="K81">
+        <v>-73.556242028856701</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>353</v>
+      </c>
+      <c r="B82" t="s">
+        <v>354</v>
+      </c>
+      <c r="C82" t="s">
+        <v>42</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82" t="s">
+        <v>355</v>
+      </c>
+      <c r="F82" t="s">
+        <v>200</v>
+      </c>
+      <c r="G82" s="2">
+        <v>46235</v>
+      </c>
+      <c r="H82" t="s">
+        <v>54</v>
+      </c>
+      <c r="I82" t="s">
+        <v>356</v>
+      </c>
+      <c r="J82">
+        <v>45.400200832169602</v>
+      </c>
+      <c r="K82">
+        <v>-75.682826499993595</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>362</v>
+      </c>
+      <c r="B83" t="s">
+        <v>363</v>
+      </c>
+      <c r="C83" t="s">
+        <v>42</v>
+      </c>
+      <c r="D83" t="s">
+        <v>204</v>
+      </c>
+      <c r="E83" t="s">
+        <v>364</v>
+      </c>
+      <c r="F83" t="s">
+        <v>30</v>
+      </c>
+      <c r="G83" t="s">
+        <v>101</v>
+      </c>
+      <c r="H83" t="s">
+        <v>54</v>
+      </c>
+      <c r="I83" t="s">
+        <v>365</v>
+      </c>
+      <c r="J83">
+        <v>45.516880077534204</v>
+      </c>
+      <c r="K83">
+        <v>-73.578516699995703</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>357</v>
+      </c>
+      <c r="B84" t="s">
+        <v>358</v>
+      </c>
+      <c r="C84" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" t="s">
+        <v>45</v>
+      </c>
+      <c r="E84" t="s">
+        <v>359</v>
+      </c>
+      <c r="F84" t="s">
+        <v>30</v>
+      </c>
+      <c r="G84" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H84" t="s">
+        <v>54</v>
+      </c>
+      <c r="I84" t="s">
+        <v>360</v>
+      </c>
+      <c r="J84">
+        <v>45.515690293055599</v>
+      </c>
+      <c r="K84">
+        <v>-73.5773859154761</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>374</v>
+      </c>
+      <c r="B85" t="s">
+        <v>375</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" t="s">
+        <v>359</v>
+      </c>
+      <c r="F85" t="s">
+        <v>30</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H85" t="s">
+        <v>54</v>
+      </c>
+      <c r="I85" t="s">
+        <v>372</v>
+      </c>
+      <c r="J85">
+        <v>45.515690293055599</v>
+      </c>
+      <c r="K85">
+        <v>-73.5773859154761</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>376</v>
+      </c>
+      <c r="B86" t="s">
+        <v>369</v>
+      </c>
+      <c r="C86" t="s">
+        <v>42</v>
+      </c>
+      <c r="D86" t="s">
+        <v>45</v>
+      </c>
+      <c r="E86" t="s">
+        <v>370</v>
+      </c>
+      <c r="F86" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45413</v>
+      </c>
+      <c r="H86" t="s">
+        <v>54</v>
+      </c>
+      <c r="I86" t="s">
+        <v>371</v>
+      </c>
+      <c r="J86">
+        <v>45.519606357024003</v>
+      </c>
+      <c r="K86">
+        <v>-73.584541108744205</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>373</v>
+      </c>
+      <c r="B87" t="s">
+        <v>377</v>
+      </c>
+      <c r="C87" t="s">
+        <v>42</v>
+      </c>
+      <c r="D87" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" t="s">
+        <v>378</v>
+      </c>
+      <c r="F87" t="s">
+        <v>30</v>
+      </c>
+      <c r="G87" t="s">
+        <v>101</v>
+      </c>
+      <c r="H87" t="s">
+        <v>54</v>
+      </c>
+      <c r="I87" t="s">
+        <v>379</v>
+      </c>
+      <c r="J87">
+        <v>45.521740114288001</v>
+      </c>
+      <c r="K87">
+        <v>-73.574832397989098</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>380</v>
+      </c>
+      <c r="B88" t="s">
+        <v>395</v>
+      </c>
+      <c r="C88" t="s">
         <v>10</v>
       </c>
-      <c r="D71" t="s">
-        <v>34</v>
-      </c>
-      <c r="E71" t="s">
-        <v>284</v>
-      </c>
-      <c r="F71" t="s">
-        <v>30</v>
-      </c>
-      <c r="G71" t="s">
-        <v>105</v>
-      </c>
-      <c r="H71" t="s">
-        <v>56</v>
-      </c>
-      <c r="I71" t="s">
-        <v>247</v>
+      <c r="D88" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" t="s">
+        <v>381</v>
+      </c>
+      <c r="F88" t="s">
+        <v>30</v>
+      </c>
+      <c r="G88" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H88" t="s">
+        <v>54</v>
+      </c>
+      <c r="I88" t="s">
+        <v>394</v>
+      </c>
+      <c r="J88">
+        <v>45.524666029045001</v>
+      </c>
+      <c r="K88">
+        <v>-73.595645033201606</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>382</v>
+      </c>
+      <c r="B89" t="s">
+        <v>383</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" t="s">
+        <v>22</v>
+      </c>
+      <c r="E89" t="s">
+        <v>384</v>
+      </c>
+      <c r="F89" t="s">
+        <v>30</v>
+      </c>
+      <c r="G89" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H89" t="s">
+        <v>54</v>
+      </c>
+      <c r="I89" t="s">
+        <v>391</v>
+      </c>
+      <c r="J89">
+        <v>45.527866263456701</v>
+      </c>
+      <c r="K89">
+        <v>-73.598379211750697</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>385</v>
+      </c>
+      <c r="B90" t="s">
+        <v>386</v>
+      </c>
+      <c r="C90" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" t="s">
+        <v>58</v>
+      </c>
+      <c r="E90" t="s">
+        <v>387</v>
+      </c>
+      <c r="F90" t="s">
+        <v>30</v>
+      </c>
+      <c r="G90" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H90" t="s">
+        <v>54</v>
+      </c>
+      <c r="I90" t="s">
+        <v>392</v>
+      </c>
+      <c r="J90">
+        <v>45.533935866272699</v>
+      </c>
+      <c r="K90">
+        <v>-73.616051493211003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>388</v>
+      </c>
+      <c r="B91" t="s">
+        <v>389</v>
+      </c>
+      <c r="C91" t="s">
+        <v>64</v>
+      </c>
+      <c r="D91" t="s">
+        <v>58</v>
+      </c>
+      <c r="E91" t="s">
+        <v>390</v>
+      </c>
+      <c r="F91" t="s">
+        <v>30</v>
+      </c>
+      <c r="G91" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H91" t="s">
+        <v>54</v>
+      </c>
+      <c r="I91" t="s">
+        <v>393</v>
+      </c>
+      <c r="J91">
+        <v>45.530784710892</v>
+      </c>
+      <c r="K91">
+        <v>-73.609141107925396</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>397</v>
+      </c>
+      <c r="B92" t="s">
+        <v>445</v>
+      </c>
+      <c r="C92" t="s">
+        <v>97</v>
+      </c>
+      <c r="D92" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" t="s">
+        <v>399</v>
+      </c>
+      <c r="F92" t="s">
+        <v>30</v>
+      </c>
+      <c r="G92" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H92" t="s">
+        <v>54</v>
+      </c>
+      <c r="I92" t="s">
+        <v>398</v>
+      </c>
+      <c r="J92">
+        <v>45.518181432246401</v>
+      </c>
+      <c r="K92">
+        <v>-73.557606846256604</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>400</v>
+      </c>
+      <c r="B93" t="s">
+        <v>444</v>
+      </c>
+      <c r="C93" t="s">
+        <v>97</v>
+      </c>
+      <c r="D93" t="s">
+        <v>29</v>
+      </c>
+      <c r="E93" t="s">
+        <v>401</v>
+      </c>
+      <c r="F93" t="s">
+        <v>30</v>
+      </c>
+      <c r="G93" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H93" t="s">
+        <v>54</v>
+      </c>
+      <c r="I93" t="s">
+        <v>406</v>
+      </c>
+      <c r="J93">
+        <v>45.519605884833197</v>
+      </c>
+      <c r="K93">
+        <v>-73.555650306157204</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>402</v>
+      </c>
+      <c r="B94" t="s">
+        <v>403</v>
+      </c>
+      <c r="C94" t="s">
+        <v>80</v>
+      </c>
+      <c r="D94" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" t="s">
+        <v>404</v>
+      </c>
+      <c r="F94" t="s">
+        <v>30</v>
+      </c>
+      <c r="G94" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H94" t="s">
+        <v>54</v>
+      </c>
+      <c r="I94" t="s">
+        <v>405</v>
+      </c>
+      <c r="J94">
+        <v>45.515012087191003</v>
+      </c>
+      <c r="K94">
+        <v>-73.645281070954098</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>410</v>
+      </c>
+      <c r="B95" t="s">
+        <v>408</v>
+      </c>
+      <c r="C95" t="s">
+        <v>97</v>
+      </c>
+      <c r="D95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E95" t="s">
+        <v>407</v>
+      </c>
+      <c r="F95" t="s">
+        <v>30</v>
+      </c>
+      <c r="G95" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H95" t="s">
+        <v>54</v>
+      </c>
+      <c r="I95" t="s">
+        <v>409</v>
+      </c>
+      <c r="J95">
+        <v>45.513878632853398</v>
+      </c>
+      <c r="K95">
+        <v>-73.647277276572794</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>415</v>
+      </c>
+      <c r="B96" t="s">
+        <v>416</v>
+      </c>
+      <c r="C96" t="s">
+        <v>42</v>
+      </c>
+      <c r="D96" t="s">
+        <v>58</v>
+      </c>
+      <c r="E96" t="s">
+        <v>414</v>
+      </c>
+      <c r="F96" t="s">
+        <v>30</v>
+      </c>
+      <c r="G96" t="s">
+        <v>101</v>
+      </c>
+      <c r="H96" t="s">
+        <v>54</v>
+      </c>
+      <c r="I96" t="s">
+        <v>417</v>
+      </c>
+      <c r="J96">
+        <v>45.527212282794103</v>
+      </c>
+      <c r="K96">
+        <v>-73.602580713378899</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>411</v>
+      </c>
+      <c r="B97" t="s">
+        <v>418</v>
+      </c>
+      <c r="C97" t="s">
+        <v>64</v>
+      </c>
+      <c r="D97" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" t="s">
+        <v>422</v>
+      </c>
+      <c r="F97" t="s">
+        <v>30</v>
+      </c>
+      <c r="G97" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H97" t="s">
+        <v>54</v>
+      </c>
+      <c r="I97" t="s">
+        <v>421</v>
+      </c>
+      <c r="J97">
+        <v>45.5270565380508</v>
+      </c>
+      <c r="K97">
+        <v>-73.577154567432103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>412</v>
+      </c>
+      <c r="B98" t="s">
+        <v>419</v>
+      </c>
+      <c r="C98" t="s">
+        <v>77</v>
+      </c>
+      <c r="D98" t="s">
+        <v>29</v>
+      </c>
+      <c r="E98" t="s">
+        <v>423</v>
+      </c>
+      <c r="F98" t="s">
+        <v>30</v>
+      </c>
+      <c r="G98" t="s">
+        <v>101</v>
+      </c>
+      <c r="H98" t="s">
+        <v>54</v>
+      </c>
+      <c r="I98" t="s">
+        <v>425</v>
+      </c>
+      <c r="J98">
+        <v>45.4829859539593</v>
+      </c>
+      <c r="K98">
+        <v>-73.562509421416607</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>413</v>
+      </c>
+      <c r="B99" t="s">
+        <v>420</v>
+      </c>
+      <c r="C99" t="s">
+        <v>42</v>
+      </c>
+      <c r="D99" t="s">
+        <v>93</v>
+      </c>
+      <c r="E99" t="s">
+        <v>424</v>
+      </c>
+      <c r="F99" t="s">
+        <v>30</v>
+      </c>
+      <c r="G99" t="s">
+        <v>101</v>
+      </c>
+      <c r="H99" t="s">
+        <v>54</v>
+      </c>
+      <c r="I99" t="s">
+        <v>426</v>
+      </c>
+      <c r="J99">
+        <v>45.485940649568398</v>
+      </c>
+      <c r="K99">
+        <v>-73.553569962349201</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>429</v>
+      </c>
+      <c r="B100" t="s">
+        <v>427</v>
+      </c>
+      <c r="C100" t="s">
+        <v>77</v>
+      </c>
+      <c r="D100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" t="s">
+        <v>428</v>
+      </c>
+      <c r="F100" t="s">
+        <v>30</v>
+      </c>
+      <c r="G100" t="s">
+        <v>101</v>
+      </c>
+      <c r="H100" t="s">
+        <v>54</v>
+      </c>
+      <c r="I100" t="s">
+        <v>430</v>
+      </c>
+      <c r="J100">
+        <v>45.537348761023502</v>
+      </c>
+      <c r="K100">
+        <v>-73.612541104065599</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>431</v>
+      </c>
+      <c r="B101" t="s">
+        <v>434</v>
+      </c>
+      <c r="C101" t="s">
+        <v>42</v>
+      </c>
+      <c r="D101" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" t="s">
+        <v>432</v>
+      </c>
+      <c r="F101" t="s">
+        <v>433</v>
+      </c>
+      <c r="G101" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H101" t="s">
+        <v>54</v>
+      </c>
+      <c r="I101" t="s">
+        <v>435</v>
+      </c>
+      <c r="J101">
+        <v>40.724788540298199</v>
+      </c>
+      <c r="K101">
+        <v>-73.994557435797503</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>437</v>
+      </c>
+      <c r="B102" t="s">
+        <v>438</v>
+      </c>
+      <c r="C102" t="s">
+        <v>80</v>
+      </c>
+      <c r="D102" t="s">
+        <v>29</v>
+      </c>
+      <c r="E102" t="s">
+        <v>436</v>
+      </c>
+      <c r="F102" t="s">
+        <v>433</v>
+      </c>
+      <c r="G102" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H102" t="s">
+        <v>143</v>
+      </c>
+      <c r="I102" t="s">
+        <v>439</v>
+      </c>
+      <c r="J102">
+        <v>40.732865680441897</v>
+      </c>
+      <c r="K102">
+        <v>-73.997970040679206</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>441</v>
+      </c>
+      <c r="B103" t="s">
+        <v>442</v>
+      </c>
+      <c r="C103" t="s">
+        <v>42</v>
+      </c>
+      <c r="D103" t="s">
+        <v>58</v>
+      </c>
+      <c r="E103" t="s">
+        <v>440</v>
+      </c>
+      <c r="F103" t="s">
+        <v>30</v>
+      </c>
+      <c r="G103" s="1">
+        <v>46266</v>
+      </c>
+      <c r="H103" t="s">
+        <v>54</v>
+      </c>
+      <c r="I103" t="s">
+        <v>443</v>
+      </c>
+      <c r="J103">
+        <v>45.5226399448838</v>
+      </c>
+      <c r="K103">
+        <v>-73.561672638551698</v>
       </c>
     </row>
   </sheetData>

--- a/card_details.xlsx
+++ b/card_details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4dac5049e7ba9ed9/Documents/website/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andygarnier/Documents/GitHub/roj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="658" documentId="8_{5C20C120-E634-F746-A4E2-348821D79BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EA130C8-7D49-C546-A6CC-933F1EA8ED59}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FAB27B-685D-0941-B502-B28F7CC7C074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21000" xr2:uid="{54D88C54-7615-1740-89B4-7C3E296F3118}"/>
   </bookViews>
@@ -656,9 +656,6 @@
     <t>other</t>
   </si>
   <si>
-    <t>1/4 tandum jumpers, the luc one</t>
-  </si>
-  <si>
     <t>the first fruity coffee I ever saw, with my papa</t>
   </si>
   <si>
@@ -1377,6 +1374,9 @@
   </si>
   <si>
     <t>pourquoi</t>
+  </si>
+  <si>
+    <t>1/4 tandem jumpers, the luc one</t>
   </si>
 </sst>
 </file>
@@ -1825,10 +1825,10 @@
         <v>4</v>
       </c>
       <c r="J1" t="s">
+        <v>294</v>
+      </c>
+      <c r="K1" t="s">
         <v>295</v>
-      </c>
-      <c r="K1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1845,7 +1845,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F2" t="s">
         <v>30</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B3" t="s">
         <v>171</v>
@@ -1880,7 +1880,7 @@
         <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F3" t="s">
         <v>160</v>
@@ -1915,7 +1915,7 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F4" t="s">
         <v>35</v>
@@ -1950,7 +1950,7 @@
         <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
@@ -1962,7 +1962,7 @@
         <v>54</v>
       </c>
       <c r="I5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J5">
         <v>45.521327999999997</v>
@@ -1985,7 +1985,7 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
@@ -2020,7 +2020,7 @@
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
@@ -2055,7 +2055,7 @@
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F8" t="s">
         <v>81</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" t="s">
         <v>218</v>
-      </c>
-      <c r="B9" t="s">
-        <v>219</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
@@ -2090,7 +2090,7 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F9" t="s">
         <v>30</v>
@@ -2102,7 +2102,7 @@
         <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J9">
         <v>45.456797999999999</v>
@@ -2125,7 +2125,7 @@
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s">
         <v>121</v>
@@ -2151,7 +2151,7 @@
         <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -2160,7 +2160,7 @@
         <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C12" t="s">
         <v>42</v>
@@ -2195,7 +2195,7 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
@@ -2207,7 +2207,7 @@
         <v>54</v>
       </c>
       <c r="I12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J12">
         <v>45.509492399999999</v>
@@ -2230,7 +2230,7 @@
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F13" t="s">
         <v>35</v>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C14" t="s">
         <v>42</v>
@@ -2265,7 +2265,7 @@
         <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
@@ -2277,7 +2277,7 @@
         <v>54</v>
       </c>
       <c r="I14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J14">
         <v>45.512964799999999</v>
@@ -2300,7 +2300,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F15" t="s">
         <v>30</v>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" t="s">
         <v>209</v>
-      </c>
-      <c r="B16" t="s">
-        <v>210</v>
       </c>
       <c r="C16" t="s">
         <v>42</v>
@@ -2335,7 +2335,7 @@
         <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
@@ -2347,7 +2347,7 @@
         <v>54</v>
       </c>
       <c r="I16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J16">
         <v>45.520293000000002</v>
@@ -2361,7 +2361,7 @@
         <v>173</v>
       </c>
       <c r="B17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -2370,7 +2370,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
@@ -2405,7 +2405,7 @@
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F18" t="s">
         <v>30</v>
@@ -2440,7 +2440,7 @@
         <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F19" t="s">
         <v>30</v>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>305</v>
+      </c>
+      <c r="B20" t="s">
         <v>306</v>
-      </c>
-      <c r="B20" t="s">
-        <v>307</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -2475,7 +2475,7 @@
         <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F20" t="s">
         <v>30</v>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>211</v>
+      </c>
+      <c r="B21" t="s">
         <v>212</v>
-      </c>
-      <c r="B21" t="s">
-        <v>213</v>
       </c>
       <c r="C21" t="s">
         <v>42</v>
@@ -2510,10 +2510,10 @@
         <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G21" t="s">
         <v>101</v>
@@ -2522,7 +2522,7 @@
         <v>54</v>
       </c>
       <c r="I21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J21">
         <v>53.551524000000001</v>
@@ -2545,7 +2545,7 @@
         <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F22" t="s">
         <v>121</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" t="s">
         <v>221</v>
-      </c>
-      <c r="B23" t="s">
-        <v>222</v>
       </c>
       <c r="C23" t="s">
         <v>42</v>
@@ -2580,7 +2580,7 @@
         <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
@@ -2592,7 +2592,7 @@
         <v>54</v>
       </c>
       <c r="I23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J23">
         <v>45.538747000000001</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C24" t="s">
         <v>80</v>
@@ -2615,7 +2615,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F24" t="s">
         <v>160</v>
@@ -2627,7 +2627,7 @@
         <v>54</v>
       </c>
       <c r="I24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J24">
         <v>43.666613699999999</v>
@@ -2650,7 +2650,7 @@
         <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F25" t="s">
         <v>30</v>
@@ -2685,7 +2685,7 @@
         <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F26" t="s">
         <v>125</v>
@@ -2720,7 +2720,7 @@
         <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F27" t="s">
         <v>125</v>
@@ -2755,7 +2755,7 @@
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F28" t="s">
         <v>11</v>
@@ -2790,7 +2790,7 @@
         <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F29" t="s">
         <v>30</v>
@@ -2825,7 +2825,7 @@
         <v>58</v>
       </c>
       <c r="E30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F30" t="s">
         <v>35</v>
@@ -2860,7 +2860,7 @@
         <v>204</v>
       </c>
       <c r="E31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F31" t="s">
         <v>200</v>
@@ -2895,7 +2895,7 @@
         <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F32" t="s">
         <v>160</v>
@@ -2930,7 +2930,7 @@
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F33" t="s">
         <v>35</v>
@@ -2965,7 +2965,7 @@
         <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
@@ -3000,7 +3000,7 @@
         <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
@@ -3035,7 +3035,7 @@
         <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -3070,7 +3070,7 @@
         <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F37" t="s">
         <v>49</v>
@@ -3105,7 +3105,7 @@
         <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F38" t="s">
         <v>30</v>
@@ -3131,7 +3131,7 @@
         <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C39" t="s">
         <v>67</v>
@@ -3140,7 +3140,7 @@
         <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
@@ -3175,7 +3175,7 @@
         <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F40" t="s">
         <v>30</v>
@@ -3210,7 +3210,7 @@
         <v>58</v>
       </c>
       <c r="E41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -3245,7 +3245,7 @@
         <v>204</v>
       </c>
       <c r="E42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F42" t="s">
         <v>147</v>
@@ -3257,13 +3257,13 @@
         <v>54</v>
       </c>
       <c r="I42" t="s">
-        <v>205</v>
+        <v>445</v>
       </c>
       <c r="J42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -3280,7 +3280,7 @@
         <v>204</v>
       </c>
       <c r="E43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F43" t="s">
         <v>147</v>
@@ -3292,7 +3292,7 @@
         <v>54</v>
       </c>
       <c r="I43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J43">
         <v>40.314159841377702</v>
@@ -3315,7 +3315,7 @@
         <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F44" t="s">
         <v>30</v>
@@ -3350,7 +3350,7 @@
         <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F45" t="s">
         <v>35</v>
@@ -3385,7 +3385,7 @@
         <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F46" t="s">
         <v>121</v>
@@ -3420,7 +3420,7 @@
         <v>58</v>
       </c>
       <c r="E47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F47" t="s">
         <v>30</v>
@@ -3455,7 +3455,7 @@
         <v>93</v>
       </c>
       <c r="E48" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F48" t="s">
         <v>30</v>
@@ -3467,7 +3467,7 @@
         <v>54</v>
       </c>
       <c r="I48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J48">
         <v>45.520293000000002</v>
@@ -3490,7 +3490,7 @@
         <v>58</v>
       </c>
       <c r="E49" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F49" t="s">
         <v>49</v>
@@ -3525,7 +3525,7 @@
         <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F50" t="s">
         <v>49</v>
@@ -3560,7 +3560,7 @@
         <v>45</v>
       </c>
       <c r="E51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F51" t="s">
         <v>30</v>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>248</v>
+      </c>
+      <c r="B52" t="s">
         <v>249</v>
-      </c>
-      <c r="B52" t="s">
-        <v>250</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
@@ -3595,7 +3595,7 @@
         <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F52" t="s">
         <v>30</v>
@@ -3630,7 +3630,7 @@
         <v>58</v>
       </c>
       <c r="E53" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F53" t="s">
         <v>30</v>
@@ -3665,7 +3665,7 @@
         <v>34</v>
       </c>
       <c r="E54" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F54" t="s">
         <v>49</v>
@@ -3677,7 +3677,7 @@
         <v>54</v>
       </c>
       <c r="I54" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J54">
         <v>45.353083499999997</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>227</v>
+      </c>
+      <c r="B55" t="s">
         <v>228</v>
-      </c>
-      <c r="B55" t="s">
-        <v>229</v>
       </c>
       <c r="C55" t="s">
         <v>97</v>
@@ -3700,7 +3700,7 @@
         <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F55" t="s">
         <v>35</v>
@@ -3712,7 +3712,7 @@
         <v>54</v>
       </c>
       <c r="I55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J55">
         <v>44.653763400000003</v>
@@ -3735,7 +3735,7 @@
         <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F56" t="s">
         <v>153</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C57" t="s">
         <v>42</v>
@@ -3770,7 +3770,7 @@
         <v>29</v>
       </c>
       <c r="E57" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F57" t="s">
         <v>30</v>
@@ -3782,7 +3782,7 @@
         <v>54</v>
       </c>
       <c r="I57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J57">
         <v>45.483075999999997</v>
@@ -3796,7 +3796,7 @@
         <v>44</v>
       </c>
       <c r="B58" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
@@ -3805,7 +3805,7 @@
         <v>45</v>
       </c>
       <c r="E58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F58" t="s">
         <v>35</v>
@@ -3840,7 +3840,7 @@
         <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
@@ -3875,7 +3875,7 @@
         <v>45</v>
       </c>
       <c r="E60" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F60" t="s">
         <v>30</v>
@@ -3898,10 +3898,10 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" t="s">
         <v>231</v>
-      </c>
-      <c r="B61" t="s">
-        <v>232</v>
       </c>
       <c r="C61" t="s">
         <v>10</v>
@@ -3910,7 +3910,7 @@
         <v>34</v>
       </c>
       <c r="E61" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
@@ -3922,7 +3922,7 @@
         <v>54</v>
       </c>
       <c r="I61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J61">
         <v>45.512327999999997</v>
@@ -3933,10 +3933,10 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B62" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C62" t="s">
         <v>80</v>
@@ -3945,7 +3945,7 @@
         <v>45</v>
       </c>
       <c r="E62" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
@@ -3957,7 +3957,7 @@
         <v>54</v>
       </c>
       <c r="I62" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J62">
         <v>45.537235000000003</v>
@@ -3980,7 +3980,7 @@
         <v>22</v>
       </c>
       <c r="E63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
@@ -3995,10 +3995,10 @@
         <v>98</v>
       </c>
       <c r="J63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -4015,7 +4015,7 @@
         <v>22</v>
       </c>
       <c r="E64" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F64" t="s">
         <v>49</v>
@@ -4050,7 +4050,7 @@
         <v>34</v>
       </c>
       <c r="E65" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F65" t="s">
         <v>30</v>
@@ -4085,7 +4085,7 @@
         <v>45</v>
       </c>
       <c r="E66" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F66" t="s">
         <v>30</v>
@@ -4120,7 +4120,7 @@
         <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F67" t="s">
         <v>142</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B68" t="s">
         <v>184</v>
@@ -4155,7 +4155,7 @@
         <v>93</v>
       </c>
       <c r="E68" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F68" t="s">
         <v>30</v>
@@ -4190,7 +4190,7 @@
         <v>93</v>
       </c>
       <c r="E69" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F69" t="s">
         <v>30</v>
@@ -4225,7 +4225,7 @@
         <v>22</v>
       </c>
       <c r="E70" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F70" t="s">
         <v>30</v>
@@ -4260,7 +4260,7 @@
         <v>22</v>
       </c>
       <c r="E71" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F71" t="s">
         <v>30</v>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>312</v>
+      </c>
+      <c r="B72" t="s">
         <v>313</v>
-      </c>
-      <c r="B72" t="s">
-        <v>314</v>
       </c>
       <c r="C72" t="s">
         <v>67</v>
@@ -4295,7 +4295,7 @@
         <v>23</v>
       </c>
       <c r="E72" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F72" t="s">
         <v>35</v>
@@ -4307,7 +4307,7 @@
         <v>54</v>
       </c>
       <c r="I72" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J72">
         <v>44.636038158292799</v>
@@ -4318,10 +4318,10 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B73" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C73" t="s">
         <v>52</v>
@@ -4330,10 +4330,10 @@
         <v>22</v>
       </c>
       <c r="E73" t="s">
+        <v>317</v>
+      </c>
+      <c r="F73" t="s">
         <v>318</v>
-      </c>
-      <c r="F73" t="s">
-        <v>319</v>
       </c>
       <c r="G73" s="1">
         <v>46204</v>
@@ -4342,7 +4342,7 @@
         <v>54</v>
       </c>
       <c r="I73" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J73">
         <v>44.6432107892483</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>320</v>
+      </c>
+      <c r="B74" t="s">
         <v>321</v>
-      </c>
-      <c r="B74" t="s">
-        <v>322</v>
       </c>
       <c r="C74" t="s">
         <v>10</v>
@@ -4365,7 +4365,7 @@
         <v>22</v>
       </c>
       <c r="E74" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F74" t="s">
         <v>49</v>
@@ -4377,7 +4377,7 @@
         <v>54</v>
       </c>
       <c r="I74" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J74">
         <v>45.359008986650501</v>
@@ -4388,10 +4388,10 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>323</v>
+      </c>
+      <c r="B75" t="s">
         <v>324</v>
-      </c>
-      <c r="B75" t="s">
-        <v>325</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
@@ -4400,7 +4400,7 @@
         <v>34</v>
       </c>
       <c r="E75" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F75" t="s">
         <v>35</v>
@@ -4412,7 +4412,7 @@
         <v>54</v>
       </c>
       <c r="I75" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J75">
         <v>44.6475375031238</v>
@@ -4423,10 +4423,10 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>327</v>
+      </c>
+      <c r="B76" t="s">
         <v>328</v>
-      </c>
-      <c r="B76" t="s">
-        <v>329</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
@@ -4435,10 +4435,10 @@
         <v>58</v>
       </c>
       <c r="E76" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F76" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G76" s="1">
         <v>46204</v>
@@ -4447,7 +4447,7 @@
         <v>54</v>
       </c>
       <c r="I76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J76">
         <v>44.645134706114099</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>331</v>
+      </c>
+      <c r="B77" t="s">
         <v>332</v>
-      </c>
-      <c r="B77" t="s">
-        <v>333</v>
       </c>
       <c r="C77" t="s">
         <v>52</v>
@@ -4470,10 +4470,10 @@
         <v>93</v>
       </c>
       <c r="E77" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F77" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G77" s="1">
         <v>46204</v>
@@ -4482,7 +4482,7 @@
         <v>54</v>
       </c>
       <c r="I77" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J77">
         <v>44.643751014574804</v>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B78" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C78" t="s">
         <v>10</v>
@@ -4505,7 +4505,7 @@
         <v>93</v>
       </c>
       <c r="E78" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F78" t="s">
         <v>30</v>
@@ -4517,7 +4517,7 @@
         <v>54</v>
       </c>
       <c r="I78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J78">
         <v>45.466528144373598</v>
@@ -4528,10 +4528,10 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>340</v>
+      </c>
+      <c r="B79" t="s">
         <v>341</v>
-      </c>
-      <c r="B79" t="s">
-        <v>342</v>
       </c>
       <c r="C79" t="s">
         <v>80</v>
@@ -4540,7 +4540,7 @@
         <v>204</v>
       </c>
       <c r="E79" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F79" t="s">
         <v>30</v>
@@ -4552,7 +4552,7 @@
         <v>54</v>
       </c>
       <c r="I79" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J79">
         <v>45.543149197762901</v>
@@ -4563,10 +4563,10 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>342</v>
+      </c>
+      <c r="B80" t="s">
         <v>343</v>
-      </c>
-      <c r="B80" t="s">
-        <v>344</v>
       </c>
       <c r="C80" t="s">
         <v>97</v>
@@ -4575,7 +4575,7 @@
         <v>45</v>
       </c>
       <c r="E80" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F80" t="s">
         <v>30</v>
@@ -4587,7 +4587,7 @@
         <v>54</v>
       </c>
       <c r="I80" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J80">
         <v>45.506976522127502</v>
@@ -4598,10 +4598,10 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>348</v>
+      </c>
+      <c r="B81" t="s">
         <v>349</v>
-      </c>
-      <c r="B81" t="s">
-        <v>350</v>
       </c>
       <c r="C81" t="s">
         <v>67</v>
@@ -4610,7 +4610,7 @@
         <v>204</v>
       </c>
       <c r="E81" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F81" t="s">
         <v>30</v>
@@ -4622,7 +4622,7 @@
         <v>54</v>
       </c>
       <c r="I81" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J81">
         <v>45.518793896594701</v>
@@ -4633,10 +4633,10 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>352</v>
+      </c>
+      <c r="B82" t="s">
         <v>353</v>
-      </c>
-      <c r="B82" t="s">
-        <v>354</v>
       </c>
       <c r="C82" t="s">
         <v>42</v>
@@ -4645,7 +4645,7 @@
         <v>23</v>
       </c>
       <c r="E82" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F82" t="s">
         <v>200</v>
@@ -4657,7 +4657,7 @@
         <v>54</v>
       </c>
       <c r="I82" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J82">
         <v>45.400200832169602</v>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>361</v>
+      </c>
+      <c r="B83" t="s">
         <v>362</v>
-      </c>
-      <c r="B83" t="s">
-        <v>363</v>
       </c>
       <c r="C83" t="s">
         <v>42</v>
@@ -4680,7 +4680,7 @@
         <v>204</v>
       </c>
       <c r="E83" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F83" t="s">
         <v>30</v>
@@ -4692,7 +4692,7 @@
         <v>54</v>
       </c>
       <c r="I83" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J83">
         <v>45.516880077534204</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>356</v>
+      </c>
+      <c r="B84" t="s">
         <v>357</v>
-      </c>
-      <c r="B84" t="s">
-        <v>358</v>
       </c>
       <c r="C84" t="s">
         <v>97</v>
@@ -4715,7 +4715,7 @@
         <v>45</v>
       </c>
       <c r="E84" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F84" t="s">
         <v>30</v>
@@ -4727,7 +4727,7 @@
         <v>54</v>
       </c>
       <c r="I84" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J84">
         <v>45.515690293055599</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>373</v>
+      </c>
+      <c r="B85" t="s">
         <v>374</v>
-      </c>
-      <c r="B85" t="s">
-        <v>375</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
@@ -4750,7 +4750,7 @@
         <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F85" t="s">
         <v>30</v>
@@ -4762,7 +4762,7 @@
         <v>54</v>
       </c>
       <c r="I85" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J85">
         <v>45.515690293055599</v>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B86" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C86" t="s">
         <v>42</v>
@@ -4785,7 +4785,7 @@
         <v>45</v>
       </c>
       <c r="E86" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F86" t="s">
         <v>30</v>
@@ -4797,7 +4797,7 @@
         <v>54</v>
       </c>
       <c r="I86" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J86">
         <v>45.519606357024003</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B87" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C87" t="s">
         <v>42</v>
@@ -4820,7 +4820,7 @@
         <v>22</v>
       </c>
       <c r="E87" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F87" t="s">
         <v>30</v>
@@ -4832,7 +4832,7 @@
         <v>54</v>
       </c>
       <c r="I87" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J87">
         <v>45.521740114288001</v>
@@ -4843,10 +4843,10 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B88" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
@@ -4855,7 +4855,7 @@
         <v>22</v>
       </c>
       <c r="E88" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F88" t="s">
         <v>30</v>
@@ -4867,7 +4867,7 @@
         <v>54</v>
       </c>
       <c r="I88" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J88">
         <v>45.524666029045001</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>381</v>
+      </c>
+      <c r="B89" t="s">
         <v>382</v>
-      </c>
-      <c r="B89" t="s">
-        <v>383</v>
       </c>
       <c r="C89" t="s">
         <v>24</v>
@@ -4890,7 +4890,7 @@
         <v>22</v>
       </c>
       <c r="E89" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F89" t="s">
         <v>30</v>
@@ -4902,7 +4902,7 @@
         <v>54</v>
       </c>
       <c r="I89" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J89">
         <v>45.527866263456701</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>384</v>
+      </c>
+      <c r="B90" t="s">
         <v>385</v>
-      </c>
-      <c r="B90" t="s">
-        <v>386</v>
       </c>
       <c r="C90" t="s">
         <v>42</v>
@@ -4925,7 +4925,7 @@
         <v>58</v>
       </c>
       <c r="E90" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F90" t="s">
         <v>30</v>
@@ -4937,7 +4937,7 @@
         <v>54</v>
       </c>
       <c r="I90" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J90">
         <v>45.533935866272699</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>387</v>
+      </c>
+      <c r="B91" t="s">
         <v>388</v>
-      </c>
-      <c r="B91" t="s">
-        <v>389</v>
       </c>
       <c r="C91" t="s">
         <v>64</v>
@@ -4960,7 +4960,7 @@
         <v>58</v>
       </c>
       <c r="E91" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F91" t="s">
         <v>30</v>
@@ -4972,7 +4972,7 @@
         <v>54</v>
       </c>
       <c r="I91" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J91">
         <v>45.530784710892</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B92" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C92" t="s">
         <v>97</v>
@@ -4995,7 +4995,7 @@
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F92" t="s">
         <v>30</v>
@@ -5007,7 +5007,7 @@
         <v>54</v>
       </c>
       <c r="I92" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J92">
         <v>45.518181432246401</v>
@@ -5018,10 +5018,10 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B93" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C93" t="s">
         <v>97</v>
@@ -5030,7 +5030,7 @@
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F93" t="s">
         <v>30</v>
@@ -5042,7 +5042,7 @@
         <v>54</v>
       </c>
       <c r="I93" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J93">
         <v>45.519605884833197</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>401</v>
+      </c>
+      <c r="B94" t="s">
         <v>402</v>
-      </c>
-      <c r="B94" t="s">
-        <v>403</v>
       </c>
       <c r="C94" t="s">
         <v>80</v>
@@ -5065,7 +5065,7 @@
         <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F94" t="s">
         <v>30</v>
@@ -5077,7 +5077,7 @@
         <v>54</v>
       </c>
       <c r="I94" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J94">
         <v>45.515012087191003</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B95" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C95" t="s">
         <v>97</v>
@@ -5100,7 +5100,7 @@
         <v>22</v>
       </c>
       <c r="E95" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F95" t="s">
         <v>30</v>
@@ -5112,7 +5112,7 @@
         <v>54</v>
       </c>
       <c r="I95" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J95">
         <v>45.513878632853398</v>
@@ -5123,10 +5123,10 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>414</v>
+      </c>
+      <c r="B96" t="s">
         <v>415</v>
-      </c>
-      <c r="B96" t="s">
-        <v>416</v>
       </c>
       <c r="C96" t="s">
         <v>42</v>
@@ -5135,7 +5135,7 @@
         <v>58</v>
       </c>
       <c r="E96" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F96" t="s">
         <v>30</v>
@@ -5147,7 +5147,7 @@
         <v>54</v>
       </c>
       <c r="I96" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J96">
         <v>45.527212282794103</v>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B97" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C97" t="s">
         <v>64</v>
@@ -5170,7 +5170,7 @@
         <v>45</v>
       </c>
       <c r="E97" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F97" t="s">
         <v>30</v>
@@ -5182,7 +5182,7 @@
         <v>54</v>
       </c>
       <c r="I97" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J97">
         <v>45.5270565380508</v>
@@ -5193,10 +5193,10 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B98" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C98" t="s">
         <v>77</v>
@@ -5205,7 +5205,7 @@
         <v>29</v>
       </c>
       <c r="E98" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F98" t="s">
         <v>30</v>
@@ -5217,7 +5217,7 @@
         <v>54</v>
       </c>
       <c r="I98" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J98">
         <v>45.4829859539593</v>
@@ -5228,10 +5228,10 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B99" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C99" t="s">
         <v>42</v>
@@ -5240,7 +5240,7 @@
         <v>93</v>
       </c>
       <c r="E99" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F99" t="s">
         <v>30</v>
@@ -5252,7 +5252,7 @@
         <v>54</v>
       </c>
       <c r="I99" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J99">
         <v>45.485940649568398</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B100" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C100" t="s">
         <v>77</v>
@@ -5275,7 +5275,7 @@
         <v>45</v>
       </c>
       <c r="E100" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F100" t="s">
         <v>30</v>
@@ -5287,7 +5287,7 @@
         <v>54</v>
       </c>
       <c r="I100" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J100">
         <v>45.537348761023502</v>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B101" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C101" t="s">
         <v>42</v>
@@ -5310,10 +5310,10 @@
         <v>29</v>
       </c>
       <c r="E101" t="s">
+        <v>431</v>
+      </c>
+      <c r="F101" t="s">
         <v>432</v>
-      </c>
-      <c r="F101" t="s">
-        <v>433</v>
       </c>
       <c r="G101" s="1">
         <v>46266</v>
@@ -5322,7 +5322,7 @@
         <v>54</v>
       </c>
       <c r="I101" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J101">
         <v>40.724788540298199</v>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>436</v>
+      </c>
+      <c r="B102" t="s">
         <v>437</v>
-      </c>
-      <c r="B102" t="s">
-        <v>438</v>
       </c>
       <c r="C102" t="s">
         <v>80</v>
@@ -5345,10 +5345,10 @@
         <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F102" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G102" s="1">
         <v>46266</v>
@@ -5357,7 +5357,7 @@
         <v>143</v>
       </c>
       <c r="I102" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J102">
         <v>40.732865680441897</v>
@@ -5368,10 +5368,10 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>440</v>
+      </c>
+      <c r="B103" t="s">
         <v>441</v>
-      </c>
-      <c r="B103" t="s">
-        <v>442</v>
       </c>
       <c r="C103" t="s">
         <v>42</v>
@@ -5380,7 +5380,7 @@
         <v>58</v>
       </c>
       <c r="E103" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F103" t="s">
         <v>30</v>
@@ -5392,7 +5392,7 @@
         <v>54</v>
       </c>
       <c r="I103" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J103">
         <v>45.5226399448838</v>
